--- a/output/Data and Chart Outputs/canada_gas.xlsx
+++ b/output/Data and Chart Outputs/canada_gas.xlsx
@@ -155,6 +155,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Canada natural gas consumption by sector (StatCan) (to Jul/26)</a:t>
             </a:r>
           </a:p>
@@ -402,6 +403,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Canada natural gas production and trade (StatCan) (to Jul/26)</a:t>
             </a:r>
           </a:p>
@@ -650,6 +652,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Canada natural gas in storage, closing inventory (StatCan) - water year (Oct-Sep), data to 2026-07-31</a:t>
             </a:r>
           </a:p>
@@ -762,7 +765,7 @@
           <spPr>
             <a:ln w="19050">
               <a:solidFill>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="2A78D6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>

--- a/output/Data and Chart Outputs/canada_gas.xlsx
+++ b/output/Data and Chart Outputs/canada_gas.xlsx
@@ -21,8 +21,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="mmm/yy"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -62,11 +62,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -156,7 +155,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Canada natural gas consumption by sector (StatCan) (to Jul/26)</a:t>
+              <a:t>Canada natural gas consumption by sector (StatCan) (to Aug/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -186,12 +185,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$68</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$68</f>
+              <f>'Chart'!$B$2:$B$69</f>
             </numRef>
           </val>
         </ser>
@@ -214,12 +213,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$68</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$68</f>
+              <f>'Chart'!$C$2:$C$69</f>
             </numRef>
           </val>
         </ser>
@@ -242,12 +241,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$68</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$68</f>
+              <f>'Chart'!$D$2:$D$69</f>
             </numRef>
           </val>
         </ser>
@@ -270,12 +269,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$68</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$68</f>
+              <f>'Chart'!$E$2:$E$69</f>
             </numRef>
           </val>
         </ser>
@@ -298,12 +297,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$68</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$68</f>
+              <f>'Chart'!$F$2:$F$69</f>
             </numRef>
           </val>
         </ser>
@@ -404,7 +403,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Canada natural gas production and trade (StatCan) (to Jul/26)</a:t>
+              <a:t>Canada natural gas production and trade (StatCan) (to Aug/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -440,12 +439,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Supply'!$A$2:$A$68</f>
+              <f>'Chart - Supply'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Supply'!$B$2:$B$68</f>
+              <f>'Chart - Supply'!$B$2:$B$69</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -476,12 +475,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Supply'!$A$2:$A$68</f>
+              <f>'Chart - Supply'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Supply'!$C$2:$C$68</f>
+              <f>'Chart - Supply'!$C$2:$C$69</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -512,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Supply'!$A$2:$A$68</f>
+              <f>'Chart - Supply'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Supply'!$D$2:$D$68</f>
+              <f>'Chart - Supply'!$D$2:$D$69</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -548,12 +547,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Supply'!$A$2:$A$68</f>
+              <f>'Chart - Supply'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Supply'!$E$2:$E$68</f>
+              <f>'Chart - Supply'!$E$2:$E$69</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -653,7 +652,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Canada natural gas in storage, closing inventory (StatCan) - water year (Oct-Sep), data to 2026-07-31</a:t>
+              <a:t>Canada natural gas in storage, closing inventory (StatCan) - water year (Oct-Sep), data to 2026-08-31</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1308,6 +1307,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -1318,10 +1318,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Canada, monthly, 2019-01 to 2026-07. StatCan publishes about two to three months after the month ends.</t>
-        </is>
-      </c>
-    </row>
+          <t>Canada, monthly, 2019-01 to 2026-08. StatCan publishes about two to three months after the month ends.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -1347,7 +1348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1386,7 +1387,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1406,7 +1407,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -1426,7 +1427,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -1446,7 +1447,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1466,7 +1467,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1486,7 +1487,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1506,7 +1507,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1526,7 +1527,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1546,7 +1547,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1566,7 +1567,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1586,7 +1587,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1606,7 +1607,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -1626,7 +1627,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -1646,7 +1647,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -1666,7 +1667,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -1686,7 +1687,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -1706,7 +1707,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -1726,7 +1727,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -1746,7 +1747,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -1766,7 +1767,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -1786,7 +1787,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -1806,7 +1807,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -1826,7 +1827,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -1846,7 +1847,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -1866,7 +1867,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -1886,7 +1887,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -1906,7 +1907,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -1926,7 +1927,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -1946,7 +1947,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -1966,7 +1967,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -1986,7 +1987,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -2006,7 +2007,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -2026,7 +2027,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -2046,7 +2047,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -2066,7 +2067,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -2086,7 +2087,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -2106,7 +2107,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -2126,7 +2127,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -2146,7 +2147,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -2166,7 +2167,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -2186,7 +2187,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -2206,7 +2207,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -2226,7 +2227,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -2246,7 +2247,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -2266,7 +2267,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -2286,7 +2287,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -2306,7 +2307,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -2326,7 +2327,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -2346,7 +2347,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -2366,7 +2367,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -2386,7 +2387,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -2406,7 +2407,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -2426,7 +2427,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -2446,7 +2447,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -2466,7 +2467,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -2486,7 +2487,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -2506,7 +2507,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -2526,7 +2527,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -2546,7 +2547,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -2566,7 +2567,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -2586,7 +2587,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2606,7 +2607,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -2626,7 +2627,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -2646,7 +2647,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -2666,7 +2667,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -2686,7 +2687,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="2" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -2706,7 +2707,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -2723,6 +2724,26 @@
       </c>
       <c r="F68" t="n">
         <v>0.4955009040569556</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B69" t="n">
+        <v>0.4143476664029834</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0.4407277658492485</v>
+      </c>
+      <c r="D69" t="n">
+        <v>9.935797830263308</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.6312153915696689</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.4732879421403548</v>
       </c>
     </row>
   </sheetData>
@@ -2737,7 +2758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2771,7 +2792,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -2788,7 +2809,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -2805,7 +2826,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -2822,7 +2843,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -2839,7 +2860,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -2856,7 +2877,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -2873,7 +2894,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -2890,7 +2911,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -2907,7 +2928,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -2924,7 +2945,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -2941,7 +2962,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -2958,7 +2979,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -2975,7 +2996,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -2992,7 +3013,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -3009,7 +3030,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -3026,7 +3047,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -3043,7 +3064,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -3060,7 +3081,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -3077,7 +3098,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -3094,7 +3115,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -3111,7 +3132,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -3128,7 +3149,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -3145,7 +3166,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -3162,7 +3183,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -3179,7 +3200,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -3196,7 +3217,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -3213,7 +3234,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -3230,7 +3251,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -3247,7 +3268,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -3264,7 +3285,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -3281,7 +3302,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -3298,7 +3319,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -3315,7 +3336,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -3332,7 +3353,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -3349,7 +3370,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -3366,7 +3387,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -3383,7 +3404,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -3400,7 +3421,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -3417,7 +3438,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -3434,7 +3455,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -3451,7 +3472,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -3468,7 +3489,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -3485,7 +3506,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -3502,7 +3523,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -3519,7 +3540,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -3536,7 +3557,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -3553,7 +3574,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -3570,7 +3591,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -3587,7 +3608,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -3604,7 +3625,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -3621,7 +3642,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -3638,7 +3659,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -3655,7 +3676,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -3672,7 +3693,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -3689,7 +3710,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -3706,7 +3727,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -3723,7 +3744,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -3740,7 +3761,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -3757,7 +3778,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -3774,7 +3795,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -3791,7 +3812,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -3808,7 +3829,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -3825,7 +3846,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -3842,7 +3863,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -3859,7 +3880,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -3876,7 +3897,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="2" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -3893,7 +3914,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -3907,6 +3928,23 @@
       </c>
       <c r="E68" t="n">
         <v>7.752429653068143</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B69" t="n">
+        <v>20.23759746864052</v>
+      </c>
+      <c r="C69" t="n">
+        <v>2.616609221380947</v>
+      </c>
+      <c r="D69" t="n">
+        <v>8.607363826421064</v>
+      </c>
+      <c r="E69" t="n">
+        <v>7.466415696688892</v>
       </c>
     </row>
   </sheetData>
@@ -11646,6 +11684,9 @@
       <c r="F306" t="n">
         <v>925.1900000000001</v>
       </c>
+      <c r="G306" t="n">
+        <v>913.47</v>
+      </c>
       <c r="H306" t="inlineStr">
         <is>
           <t>01-Aug</t>
@@ -11673,6 +11714,9 @@
       <c r="F307" t="n">
         <v>927.46</v>
       </c>
+      <c r="G307" t="n">
+        <v>916.08</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -11695,6 +11739,9 @@
       <c r="F308" t="n">
         <v>929.73</v>
       </c>
+      <c r="G308" t="n">
+        <v>918.6900000000001</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -11717,6 +11764,9 @@
       <c r="F309" t="n">
         <v>932</v>
       </c>
+      <c r="G309" t="n">
+        <v>921.29</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -11739,6 +11789,9 @@
       <c r="F310" t="n">
         <v>934.27</v>
       </c>
+      <c r="G310" t="n">
+        <v>923.9</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -11761,6 +11814,9 @@
       <c r="F311" t="n">
         <v>936.54</v>
       </c>
+      <c r="G311" t="n">
+        <v>926.51</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -11783,6 +11839,9 @@
       <c r="F312" t="n">
         <v>938.8099999999999</v>
       </c>
+      <c r="G312" t="n">
+        <v>929.11</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -11805,6 +11864,9 @@
       <c r="F313" t="n">
         <v>941.08</v>
       </c>
+      <c r="G313" t="n">
+        <v>931.72</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -11827,6 +11889,9 @@
       <c r="F314" t="n">
         <v>943.35</v>
       </c>
+      <c r="G314" t="n">
+        <v>934.33</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -11849,6 +11914,9 @@
       <c r="F315" t="n">
         <v>945.62</v>
       </c>
+      <c r="G315" t="n">
+        <v>936.9299999999999</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -11871,6 +11939,9 @@
       <c r="F316" t="n">
         <v>947.89</v>
       </c>
+      <c r="G316" t="n">
+        <v>939.54</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -11893,6 +11964,9 @@
       <c r="F317" t="n">
         <v>950.16</v>
       </c>
+      <c r="G317" t="n">
+        <v>942.15</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -11915,6 +11989,9 @@
       <c r="F318" t="n">
         <v>952.4299999999999</v>
       </c>
+      <c r="G318" t="n">
+        <v>944.75</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -11937,6 +12014,9 @@
       <c r="F319" t="n">
         <v>954.7</v>
       </c>
+      <c r="G319" t="n">
+        <v>947.36</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -11959,6 +12039,9 @@
       <c r="F320" t="n">
         <v>956.97</v>
       </c>
+      <c r="G320" t="n">
+        <v>949.97</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -11981,6 +12064,9 @@
       <c r="F321" t="n">
         <v>959.24</v>
       </c>
+      <c r="G321" t="n">
+        <v>952.5700000000001</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -12003,6 +12089,9 @@
       <c r="F322" t="n">
         <v>961.51</v>
       </c>
+      <c r="G322" t="n">
+        <v>955.1799999999999</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -12025,6 +12114,9 @@
       <c r="F323" t="n">
         <v>963.78</v>
       </c>
+      <c r="G323" t="n">
+        <v>957.79</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -12047,6 +12139,9 @@
       <c r="F324" t="n">
         <v>966.05</v>
       </c>
+      <c r="G324" t="n">
+        <v>960.39</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -12069,6 +12164,9 @@
       <c r="F325" t="n">
         <v>968.3200000000001</v>
       </c>
+      <c r="G325" t="n">
+        <v>963</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -12091,6 +12189,9 @@
       <c r="F326" t="n">
         <v>970.59</v>
       </c>
+      <c r="G326" t="n">
+        <v>965.61</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -12113,6 +12214,9 @@
       <c r="F327" t="n">
         <v>972.86</v>
       </c>
+      <c r="G327" t="n">
+        <v>968.21</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -12135,6 +12239,9 @@
       <c r="F328" t="n">
         <v>975.13</v>
       </c>
+      <c r="G328" t="n">
+        <v>970.8200000000001</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -12157,6 +12264,9 @@
       <c r="F329" t="n">
         <v>977.4</v>
       </c>
+      <c r="G329" t="n">
+        <v>973.4299999999999</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -12179,6 +12289,9 @@
       <c r="F330" t="n">
         <v>979.67</v>
       </c>
+      <c r="G330" t="n">
+        <v>976.03</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -12201,6 +12314,9 @@
       <c r="F331" t="n">
         <v>981.9400000000001</v>
       </c>
+      <c r="G331" t="n">
+        <v>978.64</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -12223,6 +12339,9 @@
       <c r="F332" t="n">
         <v>984.21</v>
       </c>
+      <c r="G332" t="n">
+        <v>981.25</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -12245,6 +12364,9 @@
       <c r="F333" t="n">
         <v>986.48</v>
       </c>
+      <c r="G333" t="n">
+        <v>983.85</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -12267,6 +12389,9 @@
       <c r="F334" t="n">
         <v>988.75</v>
       </c>
+      <c r="G334" t="n">
+        <v>986.46</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -12289,6 +12414,9 @@
       <c r="F335" t="n">
         <v>991.02</v>
       </c>
+      <c r="G335" t="n">
+        <v>989.0700000000001</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -12310,6 +12438,9 @@
       </c>
       <c r="F336" t="n">
         <v>993.29</v>
+      </c>
+      <c r="G336" t="n">
+        <v>991.6799999999999</v>
       </c>
     </row>
     <row r="337">
@@ -12989,7 +13120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X92"/>
+  <dimension ref="A1:Y93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13110,6 +13241,11 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>Closing inventory, storage (mcm)</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>Closing  inventory, storage (mcm)</t>
         </is>
       </c>
@@ -13189,6 +13325,9 @@
       <c r="X2" t="n">
         <v>18951.128</v>
       </c>
+      <c r="Y2" t="n">
+        <v>18951.128</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13265,6 +13404,9 @@
       <c r="X3" t="n">
         <v>15072.795</v>
       </c>
+      <c r="Y3" t="n">
+        <v>15072.795</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13341,6 +13483,9 @@
       <c r="X4" t="n">
         <v>13330.664</v>
       </c>
+      <c r="Y4" t="n">
+        <v>13330.664</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13417,6 +13562,9 @@
       <c r="X5" t="n">
         <v>13937.302</v>
       </c>
+      <c r="Y5" t="n">
+        <v>13937.302</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13493,6 +13641,9 @@
       <c r="X6" t="n">
         <v>15552.533</v>
       </c>
+      <c r="Y6" t="n">
+        <v>15552.533</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13569,6 +13720,9 @@
       <c r="X7" t="n">
         <v>17514.295</v>
       </c>
+      <c r="Y7" t="n">
+        <v>17514.295</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13645,6 +13799,9 @@
       <c r="X8" t="n">
         <v>19096.811</v>
       </c>
+      <c r="Y8" t="n">
+        <v>19096.811</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13721,6 +13878,9 @@
       <c r="X9" t="n">
         <v>21076.878</v>
       </c>
+      <c r="Y9" t="n">
+        <v>21076.878</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13797,6 +13957,9 @@
       <c r="X10" t="n">
         <v>22879.077</v>
       </c>
+      <c r="Y10" t="n">
+        <v>22879.077</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13873,6 +14036,9 @@
       <c r="X11" t="n">
         <v>23732.824</v>
       </c>
+      <c r="Y11" t="n">
+        <v>23732.824</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -13949,6 +14115,9 @@
       <c r="X12" t="n">
         <v>22581.567</v>
       </c>
+      <c r="Y12" t="n">
+        <v>22581.567</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -14025,6 +14194,9 @@
       <c r="X13" t="n">
         <v>21134.352</v>
       </c>
+      <c r="Y13" t="n">
+        <v>21134.352</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -14101,6 +14273,9 @@
       <c r="X14" t="n">
         <v>18176.488</v>
       </c>
+      <c r="Y14" t="n">
+        <v>18176.488</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -14177,6 +14352,9 @@
       <c r="X15" t="n">
         <v>15462.031</v>
       </c>
+      <c r="Y15" t="n">
+        <v>15462.031</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -14253,6 +14431,9 @@
       <c r="X16" t="n">
         <v>14638.634</v>
       </c>
+      <c r="Y16" t="n">
+        <v>14638.634</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -14329,6 +14510,9 @@
       <c r="X17" t="n">
         <v>15560.531</v>
       </c>
+      <c r="Y17" t="n">
+        <v>15560.531</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -14405,6 +14589,9 @@
       <c r="X18" t="n">
         <v>18275.192</v>
       </c>
+      <c r="Y18" t="n">
+        <v>18275.192</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -14481,6 +14668,9 @@
       <c r="X19" t="n">
         <v>21075.478</v>
       </c>
+      <c r="Y19" t="n">
+        <v>21075.478</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -14557,6 +14747,9 @@
       <c r="X20" t="n">
         <v>23450.18</v>
       </c>
+      <c r="Y20" t="n">
+        <v>23450.18</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -14633,6 +14826,9 @@
       <c r="X21" t="n">
         <v>25409.562</v>
       </c>
+      <c r="Y21" t="n">
+        <v>25409.562</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -14709,6 +14905,9 @@
       <c r="X22" t="n">
         <v>27576.234</v>
       </c>
+      <c r="Y22" t="n">
+        <v>27576.234</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -14785,6 +14984,9 @@
       <c r="X23" t="n">
         <v>28197.774</v>
       </c>
+      <c r="Y23" t="n">
+        <v>28197.774</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -14861,6 +15063,9 @@
       <c r="X24" t="n">
         <v>27461.739</v>
       </c>
+      <c r="Y24" t="n">
+        <v>27461.739</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -14937,6 +15142,9 @@
       <c r="X25" t="n">
         <v>24351.144</v>
       </c>
+      <c r="Y25" t="n">
+        <v>24351.144</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -15013,6 +15221,9 @@
       <c r="X26" t="n">
         <v>20231.474</v>
       </c>
+      <c r="Y26" t="n">
+        <v>20231.474</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -15089,6 +15300,9 @@
       <c r="X27" t="n">
         <v>15673.494</v>
       </c>
+      <c r="Y27" t="n">
+        <v>15673.494</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -15165,6 +15379,9 @@
       <c r="X28" t="n">
         <v>14267.237</v>
       </c>
+      <c r="Y28" t="n">
+        <v>14267.237</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -15241,6 +15458,9 @@
       <c r="X29" t="n">
         <v>15000.173</v>
       </c>
+      <c r="Y29" t="n">
+        <v>15000.173</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -15317,6 +15537,9 @@
       <c r="X30" t="n">
         <v>16761.37</v>
       </c>
+      <c r="Y30" t="n">
+        <v>16761.37</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -15393,6 +15616,9 @@
       <c r="X31" t="n">
         <v>18610.093</v>
       </c>
+      <c r="Y31" t="n">
+        <v>18610.093</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -15469,6 +15695,9 @@
       <c r="X32" t="n">
         <v>20249.848</v>
       </c>
+      <c r="Y32" t="n">
+        <v>20249.848</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -15545,6 +15774,9 @@
       <c r="X33" t="n">
         <v>22109.888</v>
       </c>
+      <c r="Y33" t="n">
+        <v>22109.888</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -15621,6 +15853,9 @@
       <c r="X34" t="n">
         <v>24543.154</v>
       </c>
+      <c r="Y34" t="n">
+        <v>24543.154</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -15697,6 +15932,9 @@
       <c r="X35" t="n">
         <v>24972.324</v>
       </c>
+      <c r="Y35" t="n">
+        <v>24972.324</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -15773,6 +16011,9 @@
       <c r="X36" t="n">
         <v>24025.831</v>
       </c>
+      <c r="Y36" t="n">
+        <v>24025.831</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -15849,6 +16090,9 @@
       <c r="X37" t="n">
         <v>21540.825</v>
       </c>
+      <c r="Y37" t="n">
+        <v>21540.825</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -15925,6 +16169,9 @@
       <c r="X38" t="n">
         <v>16295.614</v>
       </c>
+      <c r="Y38" t="n">
+        <v>16295.614</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -16001,6 +16248,9 @@
       <c r="X39" t="n">
         <v>12334.472</v>
       </c>
+      <c r="Y39" t="n">
+        <v>12334.472</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -16077,6 +16327,9 @@
       <c r="X40" t="n">
         <v>11004.692</v>
       </c>
+      <c r="Y40" t="n">
+        <v>11004.692</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -16153,6 +16406,9 @@
       <c r="X41" t="n">
         <v>11019.273</v>
       </c>
+      <c r="Y41" t="n">
+        <v>11019.273</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -16229,6 +16485,9 @@
       <c r="X42" t="n">
         <v>13467.11</v>
       </c>
+      <c r="Y42" t="n">
+        <v>13467.11</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -16305,6 +16564,9 @@
       <c r="X43" t="n">
         <v>15840.398</v>
       </c>
+      <c r="Y43" t="n">
+        <v>15840.398</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -16381,6 +16643,9 @@
       <c r="X44" t="n">
         <v>18324.293</v>
       </c>
+      <c r="Y44" t="n">
+        <v>18324.293</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -16457,6 +16722,9 @@
       <c r="X45" t="n">
         <v>21065.852</v>
       </c>
+      <c r="Y45" t="n">
+        <v>21065.852</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -16533,6 +16801,9 @@
       <c r="X46" t="n">
         <v>23140.888</v>
       </c>
+      <c r="Y46" t="n">
+        <v>23140.888</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -16609,6 +16880,9 @@
       <c r="X47" t="n">
         <v>24366</v>
       </c>
+      <c r="Y47" t="n">
+        <v>24366</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -16685,6 +16959,9 @@
       <c r="X48" t="n">
         <v>23603.63</v>
       </c>
+      <c r="Y48" t="n">
+        <v>23603.63</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -16761,6 +17038,9 @@
       <c r="X49" t="n">
         <v>19870.684</v>
       </c>
+      <c r="Y49" t="n">
+        <v>19870.684</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -16837,6 +17117,9 @@
       <c r="X50" t="n">
         <v>17529.739</v>
       </c>
+      <c r="Y50" t="n">
+        <v>17529.739</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -16913,6 +17196,9 @@
       <c r="X51" t="n">
         <v>15576.625</v>
       </c>
+      <c r="Y51" t="n">
+        <v>15576.625</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -16989,6 +17275,9 @@
       <c r="X52" t="n">
         <v>14785.715</v>
       </c>
+      <c r="Y52" t="n">
+        <v>14785.715</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -17065,6 +17354,9 @@
       <c r="X53" t="n">
         <v>16356.351</v>
       </c>
+      <c r="Y53" t="n">
+        <v>16356.351</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -17141,6 +17433,9 @@
       <c r="X54" t="n">
         <v>18697.95</v>
       </c>
+      <c r="Y54" t="n">
+        <v>18697.95</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -17217,6 +17512,9 @@
       <c r="X55" t="n">
         <v>20752.137</v>
       </c>
+      <c r="Y55" t="n">
+        <v>20752.137</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -17293,6 +17591,9 @@
       <c r="X56" t="n">
         <v>22743.414</v>
       </c>
+      <c r="Y56" t="n">
+        <v>22743.414</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -17369,6 +17670,9 @@
       <c r="X57" t="n">
         <v>24954.919</v>
       </c>
+      <c r="Y57" t="n">
+        <v>24954.919</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -17445,6 +17749,9 @@
       <c r="X58" t="n">
         <v>27415.148</v>
       </c>
+      <c r="Y58" t="n">
+        <v>27415.148</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -17521,6 +17828,9 @@
       <c r="X59" t="n">
         <v>28616.787</v>
       </c>
+      <c r="Y59" t="n">
+        <v>28616.787</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -17597,6 +17907,9 @@
       <c r="X60" t="n">
         <v>27751.21</v>
       </c>
+      <c r="Y60" t="n">
+        <v>27751.21</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -17673,6 +17986,9 @@
       <c r="X61" t="n">
         <v>26823.339</v>
       </c>
+      <c r="Y61" t="n">
+        <v>26823.339</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -17749,6 +18065,9 @@
       <c r="X62" t="n">
         <v>22143.435</v>
       </c>
+      <c r="Y62" t="n">
+        <v>22143.435</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -17825,6 +18144,9 @@
       <c r="X63" t="n">
         <v>20584.514</v>
       </c>
+      <c r="Y63" t="n">
+        <v>20584.514</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -17901,6 +18223,9 @@
       <c r="X64" t="n">
         <v>20735.93</v>
       </c>
+      <c r="Y64" t="n">
+        <v>20735.93</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -17977,6 +18302,9 @@
       <c r="X65" t="n">
         <v>22267.068</v>
       </c>
+      <c r="Y65" t="n">
+        <v>22267.068</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -18053,6 +18381,9 @@
       <c r="X66" t="n">
         <v>24139.242</v>
       </c>
+      <c r="Y66" t="n">
+        <v>24139.242</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -18129,6 +18460,9 @@
       <c r="X67" t="n">
         <v>25960.973</v>
       </c>
+      <c r="Y67" t="n">
+        <v>25960.973</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -18205,6 +18539,9 @@
       <c r="X68" t="n">
         <v>26685.873</v>
       </c>
+      <c r="Y68" t="n">
+        <v>26685.873</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -18281,6 +18618,9 @@
       <c r="X69" t="n">
         <v>28193.879</v>
       </c>
+      <c r="Y69" t="n">
+        <v>28193.879</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -18357,6 +18697,9 @@
       <c r="X70" t="n">
         <v>29655.882</v>
       </c>
+      <c r="Y70" t="n">
+        <v>29655.882</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -18433,6 +18776,9 @@
       <c r="X71" t="n">
         <v>30545.409</v>
       </c>
+      <c r="Y71" t="n">
+        <v>30545.409</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -18509,6 +18855,9 @@
       <c r="X72" t="n">
         <v>29670.854</v>
       </c>
+      <c r="Y72" t="n">
+        <v>29670.854</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -18585,6 +18934,9 @@
       <c r="X73" t="n">
         <v>27349.283</v>
       </c>
+      <c r="Y73" t="n">
+        <v>27349.283</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -18661,6 +19013,9 @@
       <c r="X74" t="n">
         <v>22693.823</v>
       </c>
+      <c r="Y74" t="n">
+        <v>22693.823</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -18737,6 +19092,9 @@
       <c r="X75" t="n">
         <v>18696.518</v>
       </c>
+      <c r="Y75" t="n">
+        <v>18696.518</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -18813,6 +19171,9 @@
       <c r="X76" t="n">
         <v>18555.254</v>
       </c>
+      <c r="Y76" t="n">
+        <v>18555.254</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -18889,6 +19250,9 @@
       <c r="X77" t="n">
         <v>19547.726</v>
       </c>
+      <c r="Y77" t="n">
+        <v>19547.726</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -18965,6 +19329,9 @@
       <c r="X78" t="n">
         <v>22508.866</v>
       </c>
+      <c r="Y78" t="n">
+        <v>22508.866</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -19041,6 +19408,9 @@
       <c r="X79" t="n">
         <v>24510.352</v>
       </c>
+      <c r="Y79" t="n">
+        <v>24510.352</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -19117,6 +19487,9 @@
       <c r="X80" t="n">
         <v>26134.03</v>
       </c>
+      <c r="Y80" t="n">
+        <v>26134.03</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -19193,6 +19566,9 @@
       <c r="X81" t="n">
         <v>28126.878</v>
       </c>
+      <c r="Y81" t="n">
+        <v>28126.878</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -19269,6 +19645,9 @@
       <c r="X82" t="n">
         <v>30015.017</v>
       </c>
+      <c r="Y82" t="n">
+        <v>30015.017</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -19345,6 +19724,9 @@
       <c r="X83" t="n">
         <v>31025.428</v>
       </c>
+      <c r="Y83" t="n">
+        <v>31025.428</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -19421,6 +19803,9 @@
       <c r="X84" t="n">
         <v>30025.072</v>
       </c>
+      <c r="Y84" t="n">
+        <v>30025.072</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -19497,6 +19882,9 @@
       <c r="X85" t="n">
         <v>26575.205</v>
       </c>
+      <c r="Y85" t="n">
+        <v>26575.205</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -19573,6 +19961,9 @@
       <c r="X86" t="n">
         <v>22156.327</v>
       </c>
+      <c r="Y86" t="n">
+        <v>22156.327</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -19649,6 +20040,9 @@
       <c r="X87" t="n">
         <v>19479.1</v>
       </c>
+      <c r="Y87" t="n">
+        <v>19479.1</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -19725,6 +20119,9 @@
       <c r="X88" t="n">
         <v>19035.711</v>
       </c>
+      <c r="Y88" t="n">
+        <v>19035.711</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -19801,6 +20198,9 @@
       <c r="X89" t="n">
         <v>19516.099</v>
       </c>
+      <c r="Y89" t="n">
+        <v>19516.099</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -19877,6 +20277,9 @@
       <c r="X90" t="n">
         <v>21882.707</v>
       </c>
+      <c r="Y90" t="n">
+        <v>21882.707</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -19953,6 +20356,9 @@
       <c r="X91" t="n">
         <v>23936.481</v>
       </c>
+      <c r="Y91" t="n">
+        <v>23936.481</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -20028,6 +20434,85 @@
       </c>
       <c r="X92" t="n">
         <v>25792.776</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>25792.776</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>73.816</v>
+      </c>
+      <c r="C93" t="n">
+        <v>72.367</v>
+      </c>
+      <c r="D93" t="n">
+        <v>2.503</v>
+      </c>
+      <c r="E93" t="n">
+        <v>3.952</v>
+      </c>
+      <c r="F93" t="n">
+        <v>670.872</v>
+      </c>
+      <c r="G93" t="n">
+        <v>573.064</v>
+      </c>
+      <c r="H93" t="n">
+        <v>74.09399999999999</v>
+      </c>
+      <c r="I93" t="n">
+        <v>73.788</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="K93" t="n">
+        <v>243.733</v>
+      </c>
+      <c r="L93" t="n">
+        <v>211.425</v>
+      </c>
+      <c r="M93" t="n">
+        <v>32.308</v>
+      </c>
+      <c r="N93" t="n">
+        <v>305.563</v>
+      </c>
+      <c r="O93" t="n">
+        <v>11.733</v>
+      </c>
+      <c r="P93" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>281.35</v>
+      </c>
+      <c r="R93" t="n">
+        <v>220.424</v>
+      </c>
+      <c r="S93" t="n">
+        <v>60.899</v>
+      </c>
+      <c r="T93" t="n">
+        <v>17.874</v>
+      </c>
+      <c r="U93" t="n">
+        <v>13.402</v>
+      </c>
+      <c r="V93" t="n">
+        <v>3.237</v>
+      </c>
+      <c r="W93" t="n">
+        <v>25792.776</v>
+      </c>
+      <c r="X93" t="n">
+        <v>28081.063</v>
       </c>
     </row>
   </sheetData>
